--- a/ig/DM-JUIN-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1127">
   <si>
     <t>Property</t>
   </si>
@@ -733,12 +733,6 @@
   </si>
   <si>
     <t>Urgences Médico-Psychologiques (CUMP)</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>Urgences spécialisées cardiologiques</t>
   </si>
   <si>
     <t>152</t>
@@ -3661,7 +3655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B552"/>
+  <dimension ref="A1:B551"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -8065,23 +8059,15 @@
         <v>1124</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="s" s="2">
-        <v>1127</v>
-      </c>
-      <c r="B552" t="s" s="2">
-        <v>1128</v>
       </c>
     </row>
   </sheetData>
